--- a/media_catalog_populated.xlsx
+++ b/media_catalog_populated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6cf37664c44e90ff/Documenten/GitHub/lelibrambas-tv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="11_A3E50E8D73AF1A5640C355E481D0318BF294872A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F71BD0D-F032-4320-AB57-315CBDE0CC93}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="11_A3E50E8D73AF1A5640C355E481D0318BF294872A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6166BDA4-EAEC-45DE-8BFA-40E3AB2AE520}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="128">
   <si>
     <t>id</t>
   </si>
@@ -259,9 +259,6 @@
     <t>EVENTS</t>
   </si>
   <si>
-    <t>OTHER</t>
-  </si>
-  <si>
     <t>OTHERS</t>
   </si>
   <si>
@@ -388,17 +385,32 @@
     <t>https://customer-7c4f4yyof6wqvjv2.cloudflarestream.com/c5b8875e0ea63ad25b4f1db4d5560f48/watch</t>
   </si>
   <si>
-    <t>UPLOAD PENDING</t>
-  </si>
-  <si>
-    <t>https://customer-7c4f4yyof6wqvjv2.cloudflarestream.com/600ac01e351504396ee3e3a79b938800/watch</t>
+    <t>Zomervakanties (2001-2004)</t>
+  </si>
+  <si>
+    <t>https://customer-7c4f4yyof6wqvjv2.cloudflarestream.com/48c393b59bdd7e8208ad2e6b1133a593/watch</t>
+  </si>
+  <si>
+    <t>https://customer-7c4f4yyof6wqvjv2.cloudflarestream.com/eb9f7a0f135e267bbd086fc6f323e0aa/watch</t>
+  </si>
+  <si>
+    <t>https://customer-7c4f4yyof6wqvjv2.cloudflarestream.com/53e348c1cc577f57e567fb9b3c64538a/watch</t>
+  </si>
+  <si>
+    <t>Bram Albertus Peters (1997)</t>
+  </si>
+  <si>
+    <t>https://customer-7c4f4yyof6wqvjv2.cloudflarestream.com/4b62183a08dc2db7c90eccbb4db5ab35/watch</t>
+  </si>
+  <si>
+    <t>Eline Maria Peters (1995)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -411,6 +423,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -443,11 +461,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -459,8 +478,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -494,6 +518,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -753,16 +781,16 @@
         <v>1995</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>123</v>
+        <v>81</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.4" customHeight="1">
@@ -776,16 +804,16 @@
         <v>1997</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>123</v>
+        <v>82</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.4" customHeight="1">
@@ -799,16 +827,16 @@
         <v>2001</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>123</v>
+        <v>83</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.4" customHeight="1">
@@ -828,7 +856,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>67</v>
@@ -851,7 +879,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>72</v>
@@ -874,7 +902,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>59</v>
@@ -897,7 +925,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>63</v>
@@ -920,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>68</v>
@@ -943,7 +971,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>61</v>
@@ -966,7 +994,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>73</v>
@@ -989,10 +1017,10 @@
         <v>12</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.4" customHeight="1">
@@ -1012,7 +1040,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>70</v>
@@ -1035,7 +1063,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>77</v>
@@ -1058,7 +1086,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>66</v>
@@ -1081,7 +1109,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>74</v>
@@ -1098,15 +1126,15 @@
         <v>2005</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>122</v>
+        <v>23</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1127,10 +1155,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.4" customHeight="1">
@@ -1150,10 +1178,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.4" customHeight="1">
@@ -1173,7 +1201,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>57</v>
@@ -1196,7 +1224,7 @@
         <v>12</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>53</v>
@@ -1219,7 +1247,7 @@
         <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>45</v>
@@ -1242,7 +1270,7 @@
         <v>78</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>55</v>
@@ -1265,7 +1293,7 @@
         <v>78</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>56</v>
@@ -1288,10 +1316,10 @@
         <v>78</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="13.4" customHeight="1">
@@ -1311,7 +1339,7 @@
         <v>78</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>46</v>
@@ -1334,7 +1362,7 @@
         <v>78</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>47</v>
@@ -1357,7 +1385,7 @@
         <v>78</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>49</v>
@@ -1380,7 +1408,7 @@
         <v>78</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>60</v>
@@ -1400,10 +1428,10 @@
         <v>35</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>54</v>
@@ -1423,10 +1451,10 @@
         <v>36</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>52</v>
@@ -1449,7 +1477,7 @@
         <v>78</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>51</v>
@@ -1472,7 +1500,7 @@
         <v>79</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>76</v>
@@ -1495,10 +1523,10 @@
         <v>79</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="13.4" customHeight="1">
@@ -1518,7 +1546,7 @@
         <v>79</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>71</v>
@@ -1541,7 +1569,7 @@
         <v>79</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>69</v>
@@ -1564,7 +1592,7 @@
         <v>79</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>58</v>
@@ -1587,7 +1615,7 @@
         <v>79</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>48</v>
@@ -1610,7 +1638,7 @@
         <v>78</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>75</v>
@@ -1633,16 +1661,22 @@
         <v>79</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G40" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G4" r:id="rId1" xr:uid="{EB3B235C-708A-4547-88B8-D3101492E5A1}"/>
+    <hyperlink ref="G17" r:id="rId2" xr:uid="{6DC9477B-3834-4F7F-8B4C-9E441EDC1ECD}"/>
+    <hyperlink ref="G3" r:id="rId3" xr:uid="{20D13AF3-36D6-4844-BC47-638183459288}"/>
+    <hyperlink ref="G2" r:id="rId4" xr:uid="{D25EEA88-8047-4DA5-AC1A-C4ECFDFFD6A8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
--- a/media_catalog_populated.xlsx
+++ b/media_catalog_populated.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="media" sheetId="1" r:id="Rdbac114005694bbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="media" sheetId="1" r:id="R7b662546812b43f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,9 +139,6 @@
     <x:t xml:space="preserve">Mas Patoxas, Spain</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">./artwork/mas_patoxas.png</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">http://customer-7c4f4yyof6wqvjv2.cloudflarestream.com/e01c167f8edda1cb540db2771ee1a6f5/watch</x:t>
   </x:si>
   <x:si>
@@ -173,9 +170,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Val Thorens, France</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">./artwork/val_thorens.png</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">https://customer-7c4f4yyof6wqvjv2.cloudflarestream.com/3418b6888d1256a94c8f8820c8e400a6/watch</x:t>
@@ -733,8 +727,8 @@
       <x:c r="D4" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>9</x:v>
+      <x:c r="E4" s="2" t="str">
+        <x:v>VAKANTIEFILMS</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
         <x:v>18</x:v>
@@ -920,11 +914,11 @@
       <x:c r="E12" s="2" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F12" s="3" t="s">
+      <x:c r="F12" s="3" t="str">
+        <x:v>./artwork/mas_patoxas_spain.png</x:v>
+      </x:c>
+      <x:c r="G12" s="2" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="G12" s="2" t="s">
-        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="13.399999618530273" customHeight="1">
@@ -932,22 +926,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C13" s="4">
         <x:v>2006</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E13" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="E13" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F13" s="3" t="s">
+      <x:c r="G13" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="G13" s="2" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="13.399999618530273" customHeight="1">
@@ -955,22 +949,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C14" s="4">
         <x:v>2002</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E14" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F14" s="3" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E14" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F14" s="3" t="s">
+      <x:c r="G14" s="2" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="G14" s="2" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="13.399999618530273" customHeight="1">
@@ -978,22 +972,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C15" s="4">
         <x:v>2001</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E15" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F15" s="3" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="E15" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F15" s="3" t="s">
+      <x:c r="G15" s="2" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="G15" s="2" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="13.399999618530273" customHeight="1">
@@ -1001,22 +995,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C16" s="4">
         <x:v>2007</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E16" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F16" s="3" t="str">
+        <x:v>./artwork/val_thorens_france.png</x:v>
+      </x:c>
+      <x:c r="G16" s="2" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="E16" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F16" s="3" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G16" s="2" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="13.399999618530273" customHeight="1">
@@ -1024,22 +1018,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C17" s="4">
         <x:v>2005</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E17" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F17" s="3" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="E17" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F17" s="3" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G17" s="6" t="s">
-        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="13.399999618530273" customHeight="1">
@@ -1047,22 +1041,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C18" s="4">
         <x:v>2002</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E18" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F18" s="3" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G18" s="2" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="E18" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F18" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G18" s="2" t="s">
-        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="13.399999618530273" customHeight="1">
@@ -1070,22 +1064,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C19" s="4">
         <x:v>2004</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E19" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F19" s="3" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G19" s="2" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="E19" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F19" s="3" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G19" s="2" t="s">
-        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="13.399999618530273" customHeight="1">
@@ -1093,22 +1087,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C20" s="4">
         <x:v>2007</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E20" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F20" s="3" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G20" s="2" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="E20" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F20" s="3" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G20" s="2" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="13.399999618530273" customHeight="1">
@@ -1116,22 +1110,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C21" s="4">
         <x:v>2008</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E21" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F21" s="3" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G21" s="2" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="E21" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F21" s="3" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G21" s="2" t="s">
-        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="13.399999618530273" customHeight="1">
@@ -1139,22 +1133,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C22" s="4">
         <x:v>2001</x:v>
       </x:c>
       <x:c r="D22" s="2" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E22" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F22" s="3" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G22" s="2" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="E22" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F22" s="3" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G22" s="2" t="s">
-        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="13.399999618530273" customHeight="1">
@@ -1162,22 +1156,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C23" s="4">
         <x:v>1994</x:v>
       </x:c>
       <x:c r="D23" s="2" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E23" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F23" s="3" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E23" s="2" t="s">
+      <x:c r="G23" s="2" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="F23" s="3" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G23" s="2" t="s">
-        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="13.399999618530273" customHeight="1">
@@ -1185,22 +1179,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B24" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C24" s="4">
         <x:v>2025</x:v>
       </x:c>
       <x:c r="D24" s="2" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E24" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F24" s="3" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G24" s="2" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="E24" s="2" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F24" s="3" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G24" s="2" t="s">
-        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="13.399999618530273" customHeight="1">
@@ -1208,22 +1202,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C25" s="4">
         <x:v>2022</x:v>
       </x:c>
       <x:c r="D25" s="2" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E25" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F25" s="3" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G25" s="2" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="E25" s="2" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F25" s="3" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G25" s="2" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="13.399999618530273" customHeight="1">
@@ -1231,22 +1225,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C26" s="4">
         <x:v>2022</x:v>
       </x:c>
       <x:c r="D26" s="2" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E26" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F26" s="3" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G26" s="2" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="E26" s="2" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F26" s="3" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G26" s="2" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="13.399999618530273" customHeight="1">
@@ -1254,22 +1248,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C27" s="4">
         <x:v>2022</x:v>
       </x:c>
       <x:c r="D27" s="2" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E27" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F27" s="3" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G27" s="2" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="E27" s="2" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F27" s="3" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="G27" s="2" t="s">
-        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="13.399999618530273" customHeight="1">
@@ -1277,22 +1271,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C28" s="4">
         <x:v>2006</x:v>
       </x:c>
       <x:c r="D28" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E28" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F28" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G28" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="13.399999618530273" customHeight="1">
@@ -1300,22 +1294,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C29" s="4">
         <x:v>2006</x:v>
       </x:c>
       <x:c r="D29" s="2" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E29" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F29" s="3" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G29" s="2" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="E29" s="2" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F29" s="3" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G29" s="2" t="s">
-        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="13.399999618530273" customHeight="1">
@@ -1323,22 +1317,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C30" s="4">
         <x:v>2004</x:v>
       </x:c>
       <x:c r="D30" s="2" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E30" s="2" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F30" s="3" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="E30" s="2" t="s">
+      <x:c r="G30" s="2" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="F30" s="3" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G30" s="2" t="s">
-        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="13.399999618530273" customHeight="1">
@@ -1346,22 +1340,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C31" s="4">
         <x:v>2013</x:v>
       </x:c>
       <x:c r="D31" s="2" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E31" s="2" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F31" s="3" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G31" s="2" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="E31" s="2" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F31" s="3" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G31" s="2" t="s">
-        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="13.399999618530273" customHeight="1">
@@ -1369,22 +1363,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C32" s="4">
         <x:v>2015</x:v>
       </x:c>
       <x:c r="D32" s="2" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E32" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F32" s="3" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G32" s="2" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="E32" s="2" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F32" s="3" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G32" s="2" t="s">
-        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="13.399999618530273" customHeight="1">
@@ -1392,22 +1386,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C33" s="4">
         <x:v>2008</x:v>
       </x:c>
       <x:c r="D33" s="2" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E33" s="2" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F33" s="3" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G33" s="2" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="E33" s="2" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F33" s="3" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G33" s="2" t="s">
-        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="13.399999618530273" customHeight="1">
@@ -1415,22 +1409,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="2" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C34" s="4">
         <x:v>2008</x:v>
       </x:c>
       <x:c r="D34" s="2" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E34" s="2" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F34" s="3" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G34" s="2" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="E34" s="2" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F34" s="3" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="G34" s="2" t="s">
-        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="13.399999618530273" customHeight="1">
@@ -1438,22 +1432,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C35" s="4">
         <x:v>2008</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E35" s="2" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F35" s="3" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G35" s="2" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="E35" s="2" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F35" s="3" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G35" s="2" t="s">
-        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="13.399999618530273" customHeight="1">
@@ -1461,22 +1455,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C36" s="4">
         <x:v>2010</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E36" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F36" s="3" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="G36" s="2" t="s">
-        <x:v>116</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="13.399999618530273" customHeight="1">
@@ -1484,22 +1478,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="2" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C37" s="4">
         <x:v>2004</x:v>
       </x:c>
       <x:c r="D37" s="2" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E37" s="2" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F37" s="3" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G37" s="2" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="E37" s="2" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F37" s="3" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G37" s="2" t="s">
-        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="13.399999618530273" customHeight="1">
@@ -1507,22 +1501,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C38" s="4">
         <x:v>2015</x:v>
       </x:c>
       <x:c r="D38" s="2" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E38" s="2" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F38" s="3" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G38" s="2" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="E38" s="2" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F38" s="3" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="G38" s="2" t="s">
-        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="13.399999618530273" customHeight="1">
@@ -1530,7 +1524,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C39" s="4">
         <x:v>2026</x:v>
@@ -1539,13 +1533,13 @@
         <x:v>We're celebrating the launch of our new streaming-service Lelibrambas+. What's to discover? Subscribe to get access to the exclusive Peters Family-archive..</x:v>
       </x:c>
       <x:c r="E39" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F39" s="3" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G39" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -1553,28 +1547,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C40">
         <x:v>2015</x:v>
       </x:c>
       <x:c r="D40" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E40" s="2" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F40" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F40" s="3" t="str">
+        <x:v>./artwork/doortje_guusje.png</x:v>
       </x:c>
       <x:c r="G40" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7b5ba39c24244fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cf3cc85f68143e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>